--- a/KeywordDrivenTest/TestData/Locators.xlsx
+++ b/KeywordDrivenTest/TestData/Locators.xlsx
@@ -1,15 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28422"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B91F09A9-5801-4F3B-A549-4014BFDC280A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C1D5085-8AD6-4B15-9E85-CC3ECA4C9587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="employee_shift_ref">Sheet1!#REF!</definedName>
+    <definedName name="hr_id">Sheet1!#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -31,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>LocatorName</t>
   </si>
@@ -66,16 +70,7 @@
     <t>xpath</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>welcomeMessage</t>
-  </si>
-  <si>
-    <t>css</t>
-  </si>
-  <si>
-    <t>.welcome-message</t>
+    <t>//*[@id='LoginForm']/div[5]/div/button</t>
   </si>
 </sst>
 </file>
@@ -456,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -512,17 +507,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
